--- a/data/2026/cjsl/fall/coney-island-cyclones-united-leopards-2015-16.xlsx
+++ b/data/2026/cjsl/fall/coney-island-cyclones-united-leopards-2015-16.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/coney-island-cyclones-united-leopards-2015-16.xlsx
+++ b/data/2026/cjsl/fall/coney-island-cyclones-united-leopards-2015-16.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6 - 4</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/coney-island-cyclones-united-leopards-2015-16.xlsx
+++ b/data/2026/cjsl/fall/coney-island-cyclones-united-leopards-2015-16.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="45.1"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="44.0"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="15.400000000000002"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,36 +175,36 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Sunday, October  4, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>09:00 EDT</t>
+          <t>13:15 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>VIP Soccer Academy 2016/2017 CJSL</t>
+          <t>Coney Island Cyclones United Leopards 2015/16</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6 - 4</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Coney Island Cyclones United Leopards 2015/16</t>
+          <t>Soricha Foot SFA 2016/17 CJSL</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Kingsborough College Field - KCC Outdoor Field</t>
+          <t>Bill Brown Playground - Bill Brown Playground</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October  4, 2026</t>
+          <t>Saturday, October 17, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>13:15 EDT</t>
+          <t>10:30 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Coney Island Cyclones United Leopards 2015/16</t>
+          <t>New York United Soccer Academy NYUSA 2015/16 CJSL</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>6 - 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Soricha Foot SFA 2016/17 CJSL</t>
+          <t>Coney Island Cyclones United Leopards 2015/16</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - Bill Brown Playground</t>
+          <t>Randalls Island Park - Randalls 51- Full Sided</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -265,21 +265,21 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 17, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>10:30 EDT</t>
+          <t>09:00 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>New York United Soccer Academy NYUSA 2015/16 CJSL</t>
+          <t>Coney Island Cyclones United Leopards 2015/16</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>Coney Island Cyclones United Leopards 2015/16</t>
+          <t>VIP Soccer Academy 2016/2017 CJSL</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Randalls Island Park - Randalls 51- Full Sided</t>
+          <t>Bill Brown Playground - Bill Brown 9v9 Full Field</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -310,21 +310,21 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Sunday, November  8, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>09:00 EDT</t>
+          <t>11:45 EST</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>Coney Island Cyclones United Leopards 2015/16</t>
+          <t>Soricha Foot SFA 2016/17 CJSL</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>VIP Soccer Academy 2016/2017 CJSL</t>
+          <t>Coney Island Cyclones United Leopards 2015/16</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - Bill Brown 9v9 Full Field</t>
+          <t>CROTONA PARK TURF FIELD #2 - CROTONA PARK </t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -349,27 +349,27 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November  8, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>11:45 EST</t>
+          <t>12:00 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>Soricha Foot SFA 2016/17 CJSL</t>
+          <t>Coney Island Cyclones United Leopards 2015/16</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Coney Island Cyclones United Leopards 2015/16</t>
+          <t>New York United Soccer Academy NYUSA 2015/16 CJSL</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>CROTONA PARK TURF FIELD #2 - CROTONA PARK </t>
+          <t>Bill Brown Playground - Bill Brown Playground</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -394,27 +394,27 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November 15, 2026</t>
+          <t>Saturday, December  5, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>12:00 EST</t>
+          <t/>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>Coney Island Cyclones United Leopards 2015/16</t>
+          <t>Veras Soccer Academy V.S.A Strongest 2016-2017 cjsl</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>New York United Soccer Academy NYUSA 2015/16 CJSL</t>
+          <t>Coney Island Cyclones United Leopards 2015/16</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - Bill Brown Playground</t>
+          <t/>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -437,29 +437,25 @@
           <t>U11 (9v9) - D2</t>
         </is>
       </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="I8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Saturday, December  5, 2026</t>
+          <t>Sunday, December  6, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>09:00 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>Veras Soccer Academy V.S.A Strongest 2016-2017 cjsl</t>
+          <t>VIP Soccer Academy 2016/2017 CJSL</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -474,7 +470,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Kingsborough College Field - KCC Outdoor Field</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -482,7 +478,11 @@
           <t>U11 (9v9) - D2</t>
         </is>
       </c>
-      <c r="I9" s="0"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Rescheduled</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>

--- a/data/2026/cjsl/fall/coney-island-cyclones-united-leopards-2015-16.xlsx
+++ b/data/2026/cjsl/fall/coney-island-cyclones-united-leopards-2015-16.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 2</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
